--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="2026_Expenses_Rough" sheetId="1" r:id="rId1"/>
+    <sheet name="Corridor_Expenses_Raw" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -13,93 +13,96 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Trip Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Truck Reg</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Amount (USD)</t>
+          <t>Fuel Expense (KES)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Toll Gate</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Driver Allowance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mileage</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>KDC 482B</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hosting</t>
+          <t>Mombasa to Nairobi</t>
         </is>
       </c>
       <c r="D2">
-        <v>412.5</v>
+        <v>42500</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Corp Visa</t>
-        </is>
+      <c r="E2">
+        <v>3200</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F2">
+        <v>5000</v>
+      </c>
+      <c r="G2">
+        <v>485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Safaricom Fiber</t>
+          <t>KDD 109F</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Nairobi to Eldoret</t>
         </is>
       </c>
       <c r="D3">
-        <v>115.0</v>
+        <v>36000</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>M-Pesa</t>
-        </is>
+      <c r="E3">
+        <v>1800</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Office internet</t>
-        </is>
+      <c r="F3">
+        <v>4500</v>
+      </c>
+      <c r="G3">
+        <v>310</v>
       </c>
     </row>
     <row r="4">
@@ -110,26 +113,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Contractor Payroll</t>
+          <t>KDC 482B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Nairobi to Mombasa</t>
         </is>
       </c>
       <c r="D4">
-        <v>2400.0</v>
+        <v>41200</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Wire</t>
-        </is>
+      <c r="E4">
+        <v>3200</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F4">
+        <v>5000</v>
+      </c>
+      <c r="G4">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -1,139 +1,624 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Corridor_Expenses_Raw" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridor_Expenses_Raw" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="3">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="5">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Trip Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Truck Reg</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fuel Expense (KES)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Toll Gate</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Driver Allowance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mileage</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>KDC 482B</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Mombasa to Nairobi</t>
         </is>
       </c>
-      <c r="D2">
+      <c r="D2" s="4" t="n">
         <v>42500</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="5" t="n">
         <v>3200</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>KDD 109F</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Nairobi to Eldoret</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D3" s="8" t="n">
         <v>36000</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9" t="n">
         <v>1800</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="9" t="n">
         <v>4500</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="8" t="n">
         <v>310</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>KDC 482B</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Nairobi to Mombasa</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D4" s="4" t="n">
         <v>41200</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5" t="n">
         <v>3200</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4" t="n">
         <v>485</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -482,140 +482,2936 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trip Date</t>
+          <t>Trip ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Truck Reg</t>
+          <t>Truck Registration</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Assigned Driver</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fuel Expense (KES)</t>
+          <t>Departure Date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Toll Gate</t>
+          <t>Origin Depot</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Driver Allowance</t>
+          <t>Destination Facility</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mileage</t>
+          <t>Cargo Weight (MT)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel Litres</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fuel Cost (KES)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fuel Station Location</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Weighbridge Stamp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Toll &amp; Gate Fees (KES)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Per Diem (KES)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>En-Route Repairs (KES)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Total Trip Expense (KES)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>TRIP-2026-1001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>KDC 482B</t>
+          <t>KCU 842P</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Mombasa to Nairobi</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>42500</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>5000</v>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>485</v>
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8401</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>94084</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>TRIP-2026-1002</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>KDD 109F</t>
+          <t>KDA 119M</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Nairobi to Eldoret</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>36000</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>4500</v>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
       </c>
       <c r="G3" s="8" t="n">
-        <v>310</v>
+        <v>27.5</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8402</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>96658</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>TRIP-2026-1003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KDC 482B</t>
+          <t>KDB 482T</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Nairobi to Mombasa</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>41200</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>5000</v>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>485</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8403</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8404</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8405</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8406</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8407</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8408</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8409</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8410</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8411</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8412</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8413</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1014</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8414</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8415</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1016</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8416</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8417</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1018</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8418</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8419</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1020</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8420</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8421</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8422</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8423</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8424</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8425</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8426</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8427</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1028</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8428</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8429</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1030</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8430</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8431</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1032</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8432</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8433</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1034</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8434</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8435</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1036</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8436</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8437</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1038</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8438</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8439</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1040</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8440</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8441</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1042</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8442</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8443</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1044</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8444</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8445</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>104380</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridor_Expenses_Raw" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +117,9 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,7 +487,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -3417,4 +3421,4648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Hash</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed SLA Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Clearance Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sign-Off Authority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 1</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:26f225e2941edef161aa2f6c</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 2</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cbf24cf636bd13f0060dcb9f</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 3</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7e9d2c48c390b6ad91212000</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 4</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e8373572c5b799b26dbf1d64</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 5</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0224b3ca080e162eabfaf6e2</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 6</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:42102aead76331061628a5c9</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 7</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a75b012a181a3d67cdab6550</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 8</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:08fcd8cf7dd2e49a73c8953d</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 9</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cdd2fc83ce78a2c4dfab1e97</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 10</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:bb4954e133d4360403f1c4e0</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 11</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e77b895fe85bd67e1ce13c40</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 12</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:daedca024db7bde069e1eca8</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 13</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:257472038fc3c4034d167761</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 14</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0a1b3b3b67c269ea2e67ff99</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 15</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:8c45d84f2b0dc68dcb0749a6</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 16</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7118bb7793a0b2b68d5d471b</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 17</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ff48645507a73412a9b0b07b</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 18</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:39d15a5e9a9a5da0b4a58407</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 19</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:10aacdae13b108f0f8a86328</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 20</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0c9063f3e0bd060b3f207474</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 21</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0bcc01063e2e91a185e85d11</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 22</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2963145e841bd2b56b30802d</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 23</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e7592cfd462bd659371fed6e</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 24</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:473a2f8d1edfb09e8845ed53</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 25</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e32170882640fa6bef339ff2</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 26</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6837b8cf55b3bee874347b80</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 27</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:040f531fc4d618f4d7eac31f</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 28</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:58ea822434c9be83a6fdd199</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 29</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d73893e899fd7eb02f605219</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 30</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:07a6b5463baa89ae389ac646</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 31</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e883f7e2041f29327fa83be5</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 32</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:656920d2eb9b7e9605d3644e</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 33</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1f7f39debf0ce76412648598</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 34</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7230cf69a89adf3ef081f403</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 35</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:46e6bd5f435b786885f03332</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 36</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:dbf277c7ad0c9b2ed1329b3a</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 37</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cc7d6a9bb609ab26c45d478a</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 38</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:416990699fe39694f130d152</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 39</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a897ec44cce69e0888ea41a3</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 40</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:114c1a1f3d4333bd83b0d46d</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 41</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:bc5e7c5e486efcea2dcf1506</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 42</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:209a12598355186f0f38db4c</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 43</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:329a18a431dee04e0177ddd0</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 44</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c748dd7ff069d69bb8403a87</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 45</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6e6f144519eb14183282bb23</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 46</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4488be4060ab34f46a13df20</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 47</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b3099c95e38439215fae23fa</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 48</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3577860a48e76d7a9cec7ce2</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 49</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7e17eac8e2a7ecc0d9f90585</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 50</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:716f99088e9de3820906af93</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 51</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:16f03695111294a2f2179559</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 52</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:948dab5037765786424d365f</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 53</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3e46f5590678b4fdca7d2f3d</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 54</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7a496e002851acb5e01697a0</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 55</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0a45743b8ef79e4d4a8c23b8</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 56</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:eb57f1be2cd648817c7235ea</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 57</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3d3a641b272f088f1a96bd33</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 58</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d4244e39c8a80b089e1d49d2</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 59</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2febc54876f03ed7e7f97639</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 60</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ae42604182bfdabae158b183</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 61</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2fa39c89d6a5d96c707ce89e</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 62</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ef88287e7e14ef065e9c802d</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 63</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:dc9430d7e5eb5d1993f944eb</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 64</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7d8272f0fa3baf850ce7ea30</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 65</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:70913ccffcacc91103ad7588</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 66</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6f7d92422b25818d26153355</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 67</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7d8af211e6907a97a43c5d96</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 68</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e3a9ba9335bc175b9b6d2687</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 69</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:aad978c690f438944f46474f</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 70</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7ad47e7349cb11b119ff2a85</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 71</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2112298e9dbc4755f28f179b</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 72</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e9c2c3728c43bee2f82063f5</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 73</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0c10c6d54652ae1c1bb6df5f</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 74</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6d87965159eff0bbc3507536</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 75</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1de110e8de8111c88bf6435d</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 76</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0354f76dfaa1e27650f734ee</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 77</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c024105a6e2e4d74f64c935f</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 78</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e5926c2be7a4cf496cc4d49c</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 79</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:88baf35a2e6965ebd5c142a9</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 80</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:96376aaf0e5e8aa6d67dec1d</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 81</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cdf7b86cfb0e44926e920675</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 82</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d81b6ac0683b2248289e0abf</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 83</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:711abce14bd383a56b3f4ab1</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 84</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7664559e4745198de31bf14c</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 85</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3b3e83735be66f4bcfbb9d07</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 86</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b435e52dbf3cd2cee39682ea</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 87</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:04d8bedb75169582deba1c79</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 88</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:515886c976a178b610ca4b2c</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 89</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1dc9952535d731a665b77227</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 90</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:fb94d095d92125c0c6f356b0</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 91</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a38221a45504579b13bb9cb4</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 92</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:68cc62d6294c5435043e5359</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 93</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:aa79ecf1e577bb04faaf66c7</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 94</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:973227bbcae636c5c001f4bd</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 95</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e6daba4c67fea6424475e145</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 96</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cdb277228cb4d16fe19d0bc1</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 97</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e4d55eb226c0bb0d4b1d1b13</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 98</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0de34271254a8ea3258ab12c</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 99</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:68a16c082fb9b28a8649973d</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 100</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:29062fc7b57f9d510ffcc82c</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 101</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:653efd56f8062542790a3851</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 102</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:446488c2bd2d3bf26b24cb0c</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 103</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b7462b3bc1da3faa5e08c68b</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 104</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d6be60fb183a382895ae43b3</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 105</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7f7deb5b8ce31c0c9432b4d3</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 106</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b4c7a7dba0ea082bba680c7e</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 107</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:69e7682d6a3b21863b8c5c85</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 108</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:eabd8e7ff5afd055c2332c54</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 109</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ef318c2adf4ddcd1559dff45</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -486,2936 +486,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trip ID</t>
+          <t>Trip Date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Truck Registration</t>
+          <t>Truck Reg</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Assigned Driver</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Departure Date</t>
+          <t>Fuel Expense (KES)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Origin Depot</t>
+          <t>Toll Gate</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Destination Facility</t>
+          <t>Driver Allowance</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Cargo Weight (MT)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Diesel Litres</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fuel Cost (KES)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fuel Station Location</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Weighbridge Stamp</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Toll &amp; Gate Fees (KES)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Driver Per Diem (KES)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>En-Route Repairs (KES)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Total Trip Expense (KES)</t>
+          <t>Mileage</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TRIP-2026-1001</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>KCU 842P</t>
+          <t>KDC 482B</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
+          <t>Mombasa to Nairobi</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>42500</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>5000</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8401</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>94084</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>TRIP-2026-1002</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>KDA 119M</t>
+          <t>KDD 109F</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
+          <t>Nairobi to Eldoret</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>4500</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8402</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9" t="n">
-        <v>96658</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TRIP-2026-1003</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KDB 482T</t>
+          <t>KDC 482B</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
+          <t>Nairobi to Mombasa</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>41200</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5000</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8403</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1004</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8404</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8405</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>104380</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1006</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>452</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8406</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>106954</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1007</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>99528</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8407</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>109528</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1008</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>81510</v>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8408</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>94010</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1009</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8409</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>94084</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1010</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8410</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>96658</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1011</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8411</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1012</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8412</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1013</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8413</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>104380</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1014</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>452</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8414</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>106954</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1015</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>99528</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8415</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>109528</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1016</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>81510</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8416</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>94010</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1017</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8417</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>94084</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1018</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8418</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>96658</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1019</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8419</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1020</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8420</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O21" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8421</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>104380</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1022</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>452</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8422</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="9" t="n">
-        <v>106954</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1023</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>99528</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8423</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>109528</v>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1024</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>81510</v>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8424</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>94010</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1025</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8425</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>94084</v>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1026</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8426</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="9" t="n">
-        <v>96658</v>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1027</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8427</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1028</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8428</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O29" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1029</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8429</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>104380</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1030</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>452</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8430</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>106954</v>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1031</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>99528</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8431</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>109528</v>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1032</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>81510</v>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8432</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>94010</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1033</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8433</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>94084</v>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1034</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8434</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="9" t="n">
-        <v>96658</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1035</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8435</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1036</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8436</t>
-        </is>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1037</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8437</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>104380</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1038</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>452</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8438</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="9" t="n">
-        <v>106954</v>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1039</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>464</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>99528</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8439</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>109528</v>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1040</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>380</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>81510</v>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8440</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O41" s="9" t="n">
-        <v>94010</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1041</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>KCU 842P</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Joseph Mutua</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>392</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>84084</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Shell Mtito Andei Corridor Stop</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8441</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>94084</v>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1042</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>KDA 119M</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Samuel Ochieng</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>404</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>86658</v>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>TotalEnergies Machakos Junction</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8442</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="9" t="n">
-        <v>96658</v>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1043</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>KDB 482T</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>David Kiprono</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>416</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>89232</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Rubis Energy Sultan Hamud</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8443</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>99232</v>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1044</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>KDD 901W</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Francis Mwangi</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Nairobi Inland Container Depot (ICD)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Mombasa Port Berth 19</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H45" s="8" t="n">
-        <v>428</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>91806</v>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>Ola Energy Voi Highway Oasis</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8444</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N45" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O45" s="9" t="n">
-        <v>104306</v>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRIP-2026-1045</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>KDF 234Q</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Peter Kamau</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Mombasa Port Container Terminal</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Nairobi ICD Embakasi</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>94380</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>National Oil Kibwezi Truck Stop</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>WB-MARIAKANI-8445</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>104380</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/dennis_old_expense_sheet.xlsx
+++ b/public/chat_files/dennis_old_expense_sheet.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -486,140 +486,2936 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trip Date</t>
+          <t>Trip ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Truck Reg</t>
+          <t>Truck Registration</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Assigned Driver</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fuel Expense (KES)</t>
+          <t>Departure Date</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Toll Gate</t>
+          <t>Origin Depot</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Driver Allowance</t>
+          <t>Destination Facility</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mileage</t>
+          <t>Cargo Weight (MT)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Diesel Litres</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fuel Cost (KES)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fuel Station Location</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Weighbridge Stamp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Toll &amp; Gate Fees (KES)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Driver Per Diem (KES)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>En-Route Repairs (KES)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Total Trip Expense (KES)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>TRIP-2026-1001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>KDC 482B</t>
+          <t>KCU 842P</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Mombasa to Nairobi</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>42500</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>5000</v>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>485</v>
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8401</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>94084</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>TRIP-2026-1002</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>KDD 109F</t>
+          <t>KDA 119M</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Nairobi to Eldoret</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>36000</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>4500</v>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
       </c>
       <c r="G3" s="8" t="n">
-        <v>310</v>
+        <v>27.5</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8402</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>96658</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>TRIP-2026-1003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>KDC 482B</t>
+          <t>KDB 482T</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Nairobi to Mombasa</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>41200</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>5000</v>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>485</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8403</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8404</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8405</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8406</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8407</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8408</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8409</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8410</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8411</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8412</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8413</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1014</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8414</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8415</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1016</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8416</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8417</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1018</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8418</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8419</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1020</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8420</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8421</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8422</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8423</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8424</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8425</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8426</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8427</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1028</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8428</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8429</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1030</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8430</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8431</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1032</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8432</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8433</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1034</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8434</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8435</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1036</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8436</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1037</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8437</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>104380</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1038</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>96954</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8438</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>106954</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1039</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>464</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>99528</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8439</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>109528</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1040</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>380</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>81510</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8440</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1041</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>KCU 842P</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Joseph Mutua</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>392</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>84084</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Shell Mtito Andei Corridor Stop</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8441</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>94084</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1042</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>KDA 119M</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Samuel Ochieng</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>86658</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>TotalEnergies Machakos Junction</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8442</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>96658</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1043</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>KDB 482T</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>David Kiprono</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>89232</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Rubis Energy Sultan Hamud</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8443</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>99232</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1044</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>KDD 901W</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Francis Mwangi</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Nairobi Inland Container Depot (ICD)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Mombasa Port Berth 19</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>428</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>91806</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Ola Energy Voi Highway Oasis</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8444</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>104306</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TRIP-2026-1045</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>KDF 234Q</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Peter Kamau</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Mombasa Port Container Terminal</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Nairobi ICD Embakasi</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>94380</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>National Oil Kibwezi Truck Stop</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>WB-MARIAKANI-8445</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>104380</v>
       </c>
     </row>
   </sheetData>
